--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487021_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487021_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.825100000000001</v>
+        <v>9.039199999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.812</v>
+        <v>6.8779</v>
       </c>
       <c r="F2" t="n">
-        <v>2.013</v>
+        <v>2.1613</v>
       </c>
       <c r="G2" t="n">
         <v>4.5748</v>
@@ -610,13 +610,13 @@
         <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5172</v>
+        <v>0.7313</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1858</v>
+        <v>0.2517</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3314</v>
+        <v>0.4796</v>
       </c>
       <c r="V2" t="n">
         <v>2.7063</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8323</v>
+        <v>8.367599999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>7.492</v>
+        <v>7.7012</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3403</v>
+        <v>0.6664</v>
       </c>
       <c r="G3" t="n">
         <v>6.7781</v>
@@ -688,13 +688,13 @@
         <v>1.8481</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2328</v>
+        <v>0.7681</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6469</v>
+        <v>0.8561</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4141</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.5375</v>
+        <v>5.442</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1799</v>
+        <v>4.8472</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3577</v>
+        <v>0.5948</v>
       </c>
       <c r="G4" t="n">
         <v>2.2837</v>
@@ -766,13 +766,13 @@
         <v>2.4641</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9048</v>
+        <v>1.8093</v>
       </c>
       <c r="T4" t="n">
-        <v>2.704</v>
+        <v>1.3713</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2008</v>
+        <v>0.4379</v>
       </c>
       <c r="V4" t="n">
         <v>0.9384</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1047</v>
+        <v>2.8141</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0374</v>
+        <v>3.7138</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9327</v>
+        <v>-0.8997000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7371</v>
+        <v>-0.8413</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1846</v>
+        <v>-0.3179</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5525</v>
+        <v>-0.5234</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0884</v>
+        <v>1.5705</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6546</v>
+        <v>1.0969</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4338</v>
+        <v>0.4736</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3513</v>
+        <v>-2.4118</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.47</v>
+        <v>-1.4148</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8813</v>
+        <v>-0.997</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4107</v>
+        <v>1.8481</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4374</v>
+        <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9569</v>
+        <v>0.6286</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9758</v>
+        <v>0.7244</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0958</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5028</v>
+        <v>2.4047</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3728</v>
+        <v>2.6641</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8701</v>
+        <v>-0.2595</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8413</v>
+        <v>-0.1577</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3179</v>
+        <v>0.4347</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5234</v>
+        <v>-0.5924</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5705</v>
+        <v>2.4779</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0969</v>
+        <v>1.7943</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4736</v>
+        <v>0.6836</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.4118</v>
+        <v>-2.6355</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4148</v>
+        <v>-1.3596</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.997</v>
+        <v>-1.2759</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3173</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>0.3834</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.06610000000000001</v>
+        <v>0.3226</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1786</v>
+        <v>0.8295</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4189</v>
+        <v>0.8295</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3684</v>
+        <v>2.3702</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5983</v>
+        <v>3.8663</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2298</v>
+        <v>-1.4961</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1577</v>
+        <v>2.4007</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4347</v>
+        <v>-1.0772</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5924</v>
+        <v>3.478</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4779</v>
+        <v>5.7567</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7943</v>
+        <v>1.5607</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6836</v>
+        <v>4.196</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.6355</v>
+        <v>-3.356</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3596</v>
+        <v>-2.6379</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2759</v>
+        <v>-0.7181</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.6122</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3176</v>
+        <v>0.6004</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3523</v>
+        <v>0.0118</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8295</v>
+        <v>0.5893</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8295</v>
+        <v>0.5893</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MUKENDI MUKENDI</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2755</v>
+        <v>2.1929</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3266</v>
+        <v>3.096</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9489</v>
+        <v>-0.9031</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1821</v>
+        <v>0.7371</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.7216</v>
+        <v>0.1846</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5395</v>
+        <v>0.5525</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7934</v>
+        <v>3.0884</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.0302</v>
+        <v>1.6546</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2368</v>
+        <v>1.4338</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3887</v>
+        <v>-2.3513</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6913</v>
+        <v>-1.47</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3027</v>
+        <v>-0.8813</v>
       </c>
       <c r="P8" t="n">
         <v>0.4107</v>
@@ -1078,19 +1078,19 @@
         <v>1.4374</v>
       </c>
       <c r="S8" t="n">
-        <v>1.9074</v>
+        <v>1.0451</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0072</v>
+        <v>1.0343</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9002</v>
+        <v>0.0108</v>
       </c>
       <c r="V8" t="n">
-        <v>2.1396</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1396</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>M. ANDREATTA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4295</v>
+        <v>2.0732</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6885</v>
+        <v>0.5774</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.259</v>
+        <v>1.4958</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4007</v>
+        <v>1.6514</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0772</v>
+        <v>-0.5874</v>
       </c>
       <c r="I9" t="n">
-        <v>3.478</v>
+        <v>2.2388</v>
       </c>
       <c r="J9" t="n">
-        <v>5.7567</v>
+        <v>2.011</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5607</v>
+        <v>0.3538</v>
       </c>
       <c r="L9" t="n">
-        <v>4.196</v>
+        <v>1.6572</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.356</v>
+        <v>-0.3596</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.6379</v>
+        <v>-0.9412</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7181</v>
+        <v>0.5816</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2321</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3285</v>
+        <v>0.8941</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5774</v>
+        <v>0.6198</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2489</v>
+        <v>0.2743</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5893</v>
+        <v>0.3491</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ANDREATTA</t>
+          <t>M. MUKENDI MUKENDI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2734</v>
+        <v>1.7542</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4299</v>
+        <v>0.0128</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7033</v>
+        <v>1.7414</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6514</v>
+        <v>-2.1821</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5874</v>
+        <v>-2.7216</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2388</v>
+        <v>0.5395</v>
       </c>
       <c r="J10" t="n">
-        <v>2.011</v>
+        <v>-1.7934</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3538</v>
+        <v>-2.0302</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6572</v>
+        <v>0.2368</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3596</v>
+        <v>-0.3887</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9412</v>
+        <v>-0.6913</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5816</v>
+        <v>0.3027</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>0.09429999999999999</v>
+        <v>1.3861</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3875</v>
+        <v>0.6934</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4818</v>
+        <v>0.6927</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3491</v>
+        <v>2.1396</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.1396</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3045</v>
+        <v>0.6545</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.379</v>
+        <v>0.0007</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6835</v>
+        <v>0.6539</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4704</v>
@@ -1312,13 +1312,13 @@
         <v>0.2053</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0198</v>
+        <v>0.3303</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3294</v>
+        <v>0.0503</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3096</v>
+        <v>0.28</v>
       </c>
       <c r="V11" t="n">
         <v>0.5893</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>36.4537</v>
+        <v>37.11259999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>32.6986</v>
+        <v>33.35740000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>3.7551</v>
+        <v>3.7552</v>
       </c>
       <c r="G12" t="n">
         <v>14.7743</v>
@@ -1381,7 +1381,7 @@
         <v>-3.4716</v>
       </c>
       <c r="P12" t="n">
-        <v>4.1068</v>
+        <v>4.106799999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.3204</v>
@@ -1390,10 +1390,10 @@
         <v>16.4274</v>
       </c>
       <c r="S12" t="n">
-        <v>8.2523</v>
+        <v>8.911199999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>5.9264</v>
+        <v>6.585100000000001</v>
       </c>
       <c r="U12" t="n">
         <v>2.3259</v>
@@ -1405,13 +1405,13 @@
         <v>9.342700000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.02250000000000002</v>
+        <v>-0.02249999999999996</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. FALL</t>
+          <t>P. LLORACH CORNELLES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0251</v>
+        <v>-0.388</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3099</v>
+        <v>-0.0659</v>
       </c>
       <c r="F13" t="n">
-        <v>0.335</v>
+        <v>-0.3221</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.904</v>
+        <v>-0.1104</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7883</v>
+        <v>-0.3893</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1157</v>
+        <v>0.2789</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2261</v>
+        <v>-0.1104</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1104</v>
+        <v>-0.3893</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1157</v>
+        <v>0.2789</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4107</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4107</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5184</v>
+        <v>-0.2295</v>
       </c>
       <c r="T13" t="n">
-        <v>0.368</v>
+        <v>-0.0659</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1504</v>
+        <v>-0.1637</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.048</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.048</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. LLORACH CORNELLES</t>
+          <t>K. OBIEKWE SAM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4176</v>
+        <v>-0.3976</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0659</v>
+        <v>1.038</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3517</v>
+        <v>-1.4356</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1104</v>
+        <v>-0.317</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3893</v>
+        <v>-0.1591</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2789</v>
+        <v>-0.1579</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.5108</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1.0901</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.4207</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1104</v>
+        <v>-1.8278</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3893</v>
+        <v>-1.2492</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2789</v>
+        <v>-0.5786</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2592</v>
+        <v>-1.203</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0659</v>
+        <v>-0.713</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1933</v>
+        <v>-0.49</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.048</v>
+        <v>0.301</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.048</v>
+        <v>0.0608</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. OBIEKWE SAM</t>
+          <t>M. FALL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.4526</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8288</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5158</v>
+        <v>0.2757</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.317</v>
+        <v>-0.904</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1591</v>
+        <v>-0.7883</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1579</v>
+        <v>-0.1157</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5108</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0901</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4207</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8278</v>
+        <v>-0.2261</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2492</v>
+        <v>-0.1104</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5786</v>
+        <v>-0.1157</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4924</v>
+        <v>0.0407</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9222</v>
+        <v>-0.0504</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5702</v>
+        <v>0.0911</v>
       </c>
       <c r="V15" t="n">
-        <v>0.301</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0608</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7571</v>
+        <v>-0.4678</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6675</v>
+        <v>0.8767</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4247</v>
+        <v>-1.3445</v>
       </c>
       <c r="G16" t="n">
         <v>1.9619</v>
@@ -1702,13 +1702,13 @@
         <v>0.8214</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.287</v>
+        <v>-0.9976</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8563</v>
+        <v>-0.6471</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4307</v>
+        <v>-0.3505</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2267</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1821</v>
+        <v>-1.1525</v>
       </c>
       <c r="E17" t="n">
         <v>-0.0464</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1357</v>
+        <v>-1.1061</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1461</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3986</v>
+        <v>-0.369</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0659</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3328</v>
+        <v>-0.3031</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6374</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.7739</v>
+        <v>-2.7651</v>
       </c>
       <c r="E18" t="n">
-        <v>1.627</v>
+        <v>1.2085</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.4008</v>
+        <v>-3.9737</v>
       </c>
       <c r="G18" t="n">
         <v>1.7065</v>
@@ -1858,13 +1858,13 @@
         <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3468</v>
+        <v>-0.3381</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4144</v>
+        <v>-0.0041</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7612</v>
+        <v>-0.334</v>
       </c>
       <c r="V18" t="n">
         <v>0.5893</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4767</v>
+        <v>-2.8997</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7997</v>
+        <v>-0.5905</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6771</v>
+        <v>-2.3092</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6445</v>
@@ -1936,13 +1936,13 @@
         <v>0.8214</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6885</v>
+        <v>-0.1114</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2558</v>
+        <v>-0.0466</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4327</v>
+        <v>-0.0649</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9384</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0655</v>
+        <v>-3.8074</v>
       </c>
       <c r="E20" t="n">
         <v>-0.9499</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1156</v>
+        <v>-2.8575</v>
       </c>
       <c r="G20" t="n">
         <v>-1.351</v>
@@ -2014,13 +2014,13 @@
         <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.277</v>
+        <v>-1.019</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2907</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9863</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. BECHT</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2998</v>
+        <v>-4.1106</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.109</v>
+        <v>1.5193</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1908</v>
+        <v>-5.6299</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.2021</v>
+        <v>-4.2148</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0576</v>
+        <v>-0.8499</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1446</v>
+        <v>-3.3649</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.2526</v>
+        <v>1.3412</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5027</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.7499</v>
+        <v>1.2759</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0505</v>
+        <v>-5.556</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.9151</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6054</v>
+        <v>-4.6409</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.6427</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5084</v>
+        <v>-0.5521</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1704</v>
+        <v>-0.0621</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6787</v>
+        <v>-0.49</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5893</v>
+        <v>-0.9864000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5893</v>
+        <v>-1.2267</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>M. BECHT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8533</v>
+        <v>-4.3416</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9963</v>
+        <v>-4.5274</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.8496</v>
+        <v>0.1858</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.2148</v>
+        <v>-3.2021</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8499</v>
+        <v>-1.0576</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.3649</v>
+        <v>-2.1446</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3412</v>
+        <v>-3.2526</v>
       </c>
       <c r="K22" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.5027</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2759</v>
+        <v>-2.7499</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.556</v>
+        <v>0.0505</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9151</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-4.6409</v>
+        <v>0.6054</v>
       </c>
       <c r="P22" t="n">
-        <v>1.6427</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2948</v>
+        <v>-0.5502</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5851</v>
+        <v>-0.248</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7096</v>
+        <v>-0.3021</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9864000000000001</v>
+        <v>-0.5893</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2267</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.939</v>
+        <v>-5.1074</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0179</v>
+        <v>-0.4949</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.9211</v>
+        <v>-4.6125</v>
       </c>
       <c r="G23" t="n">
         <v>-4.2617</v>
@@ -2248,13 +2248,13 @@
         <v>1.4374</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3672</v>
+        <v>-0.5356</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7827</v>
+        <v>-0.2597</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5845</v>
+        <v>-0.2759</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7207</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.026899999999999</v>
+        <v>-8.471500000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.9946</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.4507</v>
+        <v>-7.477</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2911</v>
@@ -2326,13 +2326,13 @@
         <v>2.2588</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1492</v>
+        <v>-0.2954</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5461</v>
+        <v>0.1277</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3969</v>
+        <v>-0.4231</v>
       </c>
       <c r="V24" t="n">
         <v>-5.0636</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-36.4538</v>
+        <v>-34.3618</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7552</v>
+        <v>-3.7554</v>
       </c>
       <c r="F25" t="n">
-        <v>-32.6986</v>
+        <v>-30.6066</v>
       </c>
       <c r="G25" t="n">
         <v>-14.7743</v>
@@ -2404,13 +2404,13 @@
         <v>12.3206</v>
       </c>
       <c r="S25" t="n">
-        <v>-8.2523</v>
+        <v>-6.160200000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.3257</v>
+        <v>-2.3258</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.9265</v>
+        <v>-3.8345</v>
       </c>
       <c r="V25" t="n">
         <v>-9.3202</v>
